--- a/Morphologischer_Kasten/Morphologischer Kasten.xlsx
+++ b/Morphologischer_Kasten/Morphologischer Kasten.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cf956fb45453526d/Dokumente/Ausbildungen/04_Systemtechnik/2_PM2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matim\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A734AB5-3FB7-46CC-B388-F80AEA42DA1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B185DD4-B6B2-4471-9DF7-F382167BBB87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{8CA297B6-AE6F-4009-A3F9-EB60137E2069}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{8CA297B6-AE6F-4009-A3F9-EB60137E2069}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t>Lösung 1</t>
   </si>
@@ -194,14 +194,23 @@
     <t>mehrere Aufnahmeplätze, welche als Speicherplätze fungieren</t>
   </si>
   <si>
-    <t>Arm?</t>
+    <t>Gelenkarm (2 DOF)</t>
+  </si>
+  <si>
+    <t>kartesisches System (X-Z)</t>
+  </si>
+  <si>
+    <t>Arm</t>
+  </si>
+  <si>
+    <t>Gelenkarm (3 DOF)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -231,6 +240,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -246,7 +262,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -435,11 +451,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -453,65 +482,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -527,7 +571,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -843,284 +887,291 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADB612A0-7CA5-4A77-A994-AB8E6AAD9A8F}">
-  <dimension ref="B3:L37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A3:L37"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="34.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="8" width="29.85546875" customWidth="1"/>
+    <col min="2" max="2" width="34.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="8" width="29.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:12" ht="21" x14ac:dyDescent="0.35">
-      <c r="B3" s="26" t="s">
+    <row r="3" spans="1:12" ht="21" x14ac:dyDescent="0.5">
+      <c r="B3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-    </row>
-    <row r="4" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="5" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="14"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+    </row>
+    <row r="4" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="5" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B5" s="10"/>
       <c r="C5" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="13" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="17" t="s">
+    <row r="6" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B6" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="19"/>
-      <c r="I6" s="16"/>
-    </row>
-    <row r="7" spans="2:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="15" t="s">
+      <c r="G6" s="17"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="6"/>
+    </row>
+    <row r="7" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="10"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="22"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
     </row>
-    <row r="8" spans="2:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="15" t="s">
+    <row r="8" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="22"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
     </row>
-    <row r="9" spans="2:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="8"/>
+    <row r="9" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="33"/>
+      <c r="B9" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="26"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="L9" s="2"/>
     </row>
-    <row r="10" spans="2:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>51</v>
+    <row r="10" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>46</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="F10" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="G10" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="H10" s="10"/>
+        <v>47</v>
+      </c>
+      <c r="F10" s="25"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="22"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
       <c r="L10" s="2"/>
     </row>
-    <row r="11" spans="2:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G11" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="H11" s="10"/>
+    <row r="11" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="H11" s="22"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="L11" s="2"/>
     </row>
-    <row r="12" spans="2:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
+    <row r="12" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="H12" s="22"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="L12" s="2"/>
     </row>
-    <row r="13" spans="2:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="F13" s="10"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="10"/>
+    <row r="13" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="G13" s="22"/>
+      <c r="H13" s="22"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="L13" s="2"/>
     </row>
-    <row r="14" spans="2:12" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="15"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="10"/>
+    <row r="14" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="22"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="22"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="L14" s="2"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B15" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
+    <row r="15" spans="1:12" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="18"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="L15" s="2"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B16" s="15" t="s">
+    <row r="16" spans="1:12" ht="16" x14ac:dyDescent="0.35">
+      <c r="B16" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
     </row>
-    <row r="17" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="24" t="s">
+    <row r="17" spans="2:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B17" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
     </row>
-    <row r="18" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -1133,7 +1184,7 @@
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
     </row>
-    <row r="19" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
@@ -1141,7 +1192,7 @@
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
     </row>
-    <row r="20" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
@@ -1154,7 +1205,7 @@
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
     </row>
-    <row r="21" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
@@ -1167,7 +1218,7 @@
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
     </row>
-    <row r="22" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
@@ -1180,7 +1231,7 @@
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
     </row>
-    <row r="23" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
@@ -1193,7 +1244,7 @@
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
     </row>
-    <row r="24" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
@@ -1206,7 +1257,7 @@
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
     </row>
-    <row r="25" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
@@ -1219,7 +1270,7 @@
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
     </row>
-    <row r="26" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
@@ -1232,7 +1283,7 @@
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
     </row>
-    <row r="27" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B27" s="1"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
@@ -1245,7 +1296,7 @@
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
     </row>
-    <row r="28" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B28" s="1"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
@@ -1258,7 +1309,7 @@
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
     </row>
-    <row r="29" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B29" s="1"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
@@ -1271,7 +1322,7 @@
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
     </row>
-    <row r="30" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B30" s="1"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
@@ -1284,7 +1335,7 @@
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
     </row>
-    <row r="31" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B31" s="1"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
@@ -1297,7 +1348,7 @@
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
     </row>
-    <row r="32" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="1"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
@@ -1310,7 +1361,7 @@
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
     </row>
-    <row r="33" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B33" s="1"/>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
@@ -1323,7 +1374,7 @@
       <c r="K33" s="2"/>
       <c r="L33" s="2"/>
     </row>
-    <row r="34" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B34" s="1"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
@@ -1336,7 +1387,7 @@
       <c r="K34" s="2"/>
       <c r="L34" s="2"/>
     </row>
-    <row r="35" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B35" s="1"/>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
@@ -1349,7 +1400,7 @@
       <c r="K35" s="2"/>
       <c r="L35" s="2"/>
     </row>
-    <row r="36" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B36" s="1"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
@@ -1362,7 +1413,7 @@
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
     </row>
-    <row r="37" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B37" s="1"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
